--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487996_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487996_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3597</v>
+        <v>14.0012</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5621</v>
+        <v>9.950900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7976</v>
+        <v>4.0503</v>
       </c>
       <c r="G2" t="n">
         <v>8.3376</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0993</v>
+        <v>1.7408</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9236</v>
+        <v>1.3124</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1757</v>
+        <v>0.4284</v>
       </c>
       <c r="V2" t="n">
         <v>1.5441</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>11.5203</v>
+        <v>10.3926</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3768</v>
+        <v>6.0525</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1436</v>
+        <v>4.3401</v>
       </c>
       <c r="G3" t="n">
         <v>5.8256</v>
@@ -688,13 +688,13 @@
         <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3578</v>
+        <v>2.23</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9075</v>
+        <v>1.5832</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4503</v>
+        <v>0.6468</v>
       </c>
       <c r="V3" t="n">
         <v>1.5441</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7079</v>
+        <v>4.4476</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4815</v>
+        <v>0.1758</v>
       </c>
       <c r="F4" t="n">
-        <v>5.2264</v>
+        <v>4.2717</v>
       </c>
       <c r="G4" t="n">
         <v>3.786</v>
@@ -766,13 +766,13 @@
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1112</v>
+        <v>1.8509</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2445</v>
+        <v>0.9389</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8667</v>
+        <v>0.912</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8144</v>
+        <v>3.7764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9661</v>
+        <v>-0.1551</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8483</v>
+        <v>3.9315</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2156</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0345</v>
+        <v>0.9695</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8188</v>
+        <v>-0.1071</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5956</v>
+        <v>-0.7832</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9489</v>
+        <v>0.4105</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6467000000000001</v>
+        <v>-1.1937</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.38</v>
+        <v>1.6456</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0856</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4656</v>
+        <v>1.0866</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9179</v>
+        <v>0.3193</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8701</v>
+        <v>0.4121</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0478</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4737</v>
+        <v>1.2071</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4737</v>
+        <v>1.2071</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8106</v>
+        <v>2.7187</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8682</v>
+        <v>2.7187</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6788</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8624000000000001</v>
+        <v>2.7187</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9695</v>
+        <v>1.5133</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1071</v>
+        <v>1.2053</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7832</v>
+        <v>2.7187</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4105</v>
+        <v>1.5133</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1937</v>
+        <v>1.2053</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6456</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0866</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6465</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.301</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3455</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7187</v>
+        <v>2.495</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7187</v>
+        <v>1.068</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.4271</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7187</v>
+        <v>0.2156</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5133</v>
+        <v>1.0345</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2053</v>
+        <v>-0.8188</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7187</v>
+        <v>1.5956</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5133</v>
+        <v>0.9489</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2053</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.38</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.0856</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.4656</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.5986</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.972</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.6266</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.661</v>
+        <v>1.7452</v>
       </c>
       <c r="E9" t="n">
         <v>0.07389999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.587</v>
+        <v>1.6713</v>
       </c>
       <c r="G9" t="n">
         <v>2.2729</v>
@@ -1156,13 +1156,13 @@
         <v>0.9911</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6119</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4247</v>
+        <v>-0.3405</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1203</v>
+        <v>1.1307</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1236</v>
+        <v>0.0218</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9966</v>
+        <v>1.1089</v>
       </c>
       <c r="G10" t="n">
         <v>0.831</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0389</v>
+        <v>-0.0284</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3671</v>
+        <v>0.2653</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.406</v>
+        <v>-0.2937</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2666</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5747</v>
+        <v>0.9033</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0698</v>
+        <v>-1.2604</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6446</v>
+        <v>2.1637</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1493</v>
+        <v>-0.3919</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3444</v>
+        <v>1.3489</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1952</v>
+        <v>-1.7409</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2361</v>
+        <v>0.0487</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2421</v>
+        <v>1.3992</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4782</v>
+        <v>-1.3505</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3854</v>
+        <v>-0.4406</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1023</v>
+        <v>-0.0503</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2831</v>
+        <v>-0.3904</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9645</v>
+        <v>-2.9733</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7751</v>
+        <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6148</v>
+        <v>1.0792</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1307</v>
+        <v>0.4571</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5159</v>
+        <v>0.6221</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3027</v>
+        <v>0.5114</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3027</v>
+        <v>-3.2736</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3.785</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3027</v>
+        <v>1.1493</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3027</v>
+        <v>1.3444</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3027</v>
+        <v>-0.2361</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3027</v>
+        <v>0.2421</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.4782</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.3854</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.1023</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.7751</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.5515</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.927</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0.3755</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. JIMÉNEZ EXPÓSITO</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>D. JIMÉNEZ EXPÓSITO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0853</v>
+        <v>0.3027</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.9111</v>
+        <v>0.3027</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8259</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4837</v>
+        <v>0.3027</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6289</v>
+        <v>0.3027</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.1126</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.1393</v>
+        <v>0.3027</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4528</v>
+        <v>0.3027</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.5921</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6556</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1761</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5205</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.9556</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0348</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3731</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3383</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1716</v>
+        <v>-0.5208</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2791</v>
+        <v>-3.3186</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1075</v>
+        <v>2.7978</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3919</v>
+        <v>-0.4837</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3489</v>
+        <v>2.6289</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7409</v>
+        <v>-3.1126</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0487</v>
+        <v>-1.1393</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3992</v>
+        <v>1.4528</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3505</v>
+        <v>-2.5921</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4406</v>
+        <v>0.6556</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0503</v>
+        <v>1.1761</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3904</v>
+        <v>-0.5205</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9733</v>
+        <v>-4.9556</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9822</v>
+        <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0043</v>
+        <v>0.5992</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5616</v>
+        <v>0.9656</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5659</v>
+        <v>-0.3664</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2071</v>
+        <v>1.5441</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2071</v>
+        <v>1.8107</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.4786</v>
+        <v>-5.0492</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.9753</v>
+        <v>-3.8547</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5033</v>
+        <v>-1.1945</v>
       </c>
       <c r="G16" t="n">
         <v>-3.286</v>
@@ -1702,13 +1702,13 @@
         <v>2.1805</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7852</v>
+        <v>0.6442</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4881</v>
+        <v>0.6324</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2971</v>
+        <v>0.0118</v>
       </c>
       <c r="V16" t="n">
         <v>-1.6145</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>38.97080000000001</v>
+        <v>38.9708</v>
       </c>
       <c r="E17" t="n">
         <v>10.6179</v>
       </c>
       <c r="F17" t="n">
-        <v>28.35300000000001</v>
+        <v>28.35289999999999</v>
       </c>
       <c r="G17" t="n">
         <v>24.2562</v>
@@ -1762,7 +1762,7 @@
         <v>3.818200000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>4.723699999999999</v>
+        <v>4.7237</v>
       </c>
       <c r="N17" t="n">
         <v>5.2602</v>
@@ -1783,10 +1783,10 @@
         <v>10.0576</v>
       </c>
       <c r="T17" t="n">
-        <v>8.278700000000001</v>
+        <v>8.2788</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7789</v>
+        <v>1.7788</v>
       </c>
       <c r="V17" t="n">
         <v>6.639100000000001</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6654</v>
+        <v>2.0576</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.487</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2989</v>
+        <v>1.5706</v>
       </c>
       <c r="G18" t="n">
         <v>0.5760999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>4.7574</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.8486</v>
+        <v>-1.4563</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.6113</v>
+        <v>-0.4907</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2373</v>
+        <v>-0.9656</v>
       </c>
       <c r="V18" t="n">
         <v>1.1538</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>F. MONTIEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3027</v>
+        <v>0.9821</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3027</v>
+        <v>1.1174</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.1352</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3027</v>
+        <v>-2.0595</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3027</v>
+        <v>-0.877</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.1825</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3027</v>
+        <v>0.0542</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3027</v>
+        <v>0.0542</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-2.1137</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.9312</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.1825</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.1439</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.5985</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. MONTIEL RODRIGUEZ</t>
+          <t>G. CABRERA RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.5004</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2005</v>
+        <v>-0.9459</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2711</v>
+        <v>1.4463</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0595</v>
+        <v>-1.8856</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.877</v>
+        <v>-1.4109</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1825</v>
+        <v>-0.4746</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0542</v>
+        <v>-1.1768</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0542</v>
+        <v>-1.217</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1137</v>
+        <v>-0.7087</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9312</v>
+        <v>-0.1939</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1825</v>
+        <v>-0.5148</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5769</v>
+        <v>2.9733</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5769</v>
+        <v>2.9733</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.795</v>
+        <v>-0.5341</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0608</v>
+        <v>-0.0357</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7343</v>
+        <v>-0.4984</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2071</v>
+        <v>-0.0533</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. CABRERA RUIZ</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5686</v>
+        <v>0.3027</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.659</v>
+        <v>0.3027</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0904</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8856</v>
+        <v>0.3027</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4109</v>
+        <v>0.3027</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4746</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1768</v>
+        <v>0.3027</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.217</v>
+        <v>0.3027</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7087</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1939</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5148</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9733</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9733</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6031</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7488</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8615</v>
+        <v>-0.8053</v>
       </c>
       <c r="E22" t="n">
         <v>-0.0241</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8374</v>
+        <v>-0.7812</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7007</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.359</v>
+        <v>-0.3029</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9779</v>
+        <v>-1.2214</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1006</v>
+        <v>-2.5081</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1228</v>
+        <v>1.2867</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0519</v>
@@ -2248,13 +2248,13 @@
         <v>2.1805</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0619</v>
+        <v>-0.3055</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5581</v>
+        <v>0.1506</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6201</v>
+        <v>-0.4562</v>
       </c>
       <c r="V23" t="n">
         <v>-0.0533</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9274</v>
+        <v>-3.3844</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8596</v>
+        <v>0.2136</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9322</v>
+        <v>-3.598</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4337</v>
+        <v>-0.5631</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0802</v>
+        <v>0.0684</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6465</v>
+        <v>-0.6314</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0687</v>
+        <v>2.4408</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.149</v>
+        <v>2.2801</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0804</v>
+        <v>0.1607</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.365</v>
+        <v>-3.0038</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9312</v>
+        <v>-2.2117</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5661</v>
+        <v>-0.7922</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.1716</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.9467</v>
+        <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7751</v>
+        <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>2.885</v>
+        <v>-1.416</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8892</v>
+        <v>-0.2449</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0042</v>
+        <v>-1.1711</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4737</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8023</v>
+        <v>-4.5741</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.092</v>
+        <v>-3.3634</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.7103</v>
+        <v>-1.2107</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5631</v>
+        <v>-1.2884</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0684</v>
+        <v>-1.4242</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6314</v>
+        <v>0.1358</v>
       </c>
       <c r="J25" t="n">
-        <v>2.4408</v>
+        <v>-1.3583</v>
       </c>
       <c r="K25" t="n">
-        <v>2.2801</v>
+        <v>-1.3583</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.0038</v>
+        <v>0.0699</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.2117</v>
+        <v>-0.066</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7922</v>
+        <v>0.1358</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1982</v>
+        <v>-1.784</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R25" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8339</v>
+        <v>-0.2946</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5505</v>
+        <v>-0.0229</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2834</v>
+        <v>-0.2717</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2071</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.6759</v>
+        <v>-5.2397</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.4653</v>
+        <v>-5.9988</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2107</v>
+        <v>0.7591</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.2884</v>
+        <v>-1.4337</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.4242</v>
+        <v>-2.0802</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1358</v>
+        <v>0.6465</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.3583</v>
+        <v>-1.0687</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.3583</v>
+        <v>-1.149</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0699</v>
+        <v>-0.365</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.066</v>
+        <v>-0.9312</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1358</v>
+        <v>0.5661</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.784</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.9822</v>
+        <v>-5.9467</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1982</v>
+        <v>2.7751</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3964</v>
+        <v>0.5727</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1248</v>
+        <v>0.75</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2717</v>
+        <v>-0.1773</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2071</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2071</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.8247</v>
+        <v>-5.8071</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.7755</v>
+        <v>-2.6737</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.0492</v>
+        <v>-3.1334</v>
       </c>
       <c r="G27" t="n">
         <v>-2.4098</v>
@@ -2560,13 +2560,13 @@
         <v>0.9911</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.4327</v>
+        <v>-1.4151</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8736</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5591</v>
+        <v>-0.6434</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-9.7905</v>
+        <v>-9.7814</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.324</v>
+        <v>-6.7314</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.4666</v>
+        <v>-3.05</v>
       </c>
       <c r="G28" t="n">
         <v>-5.741</v>
@@ -2638,13 +2638,13 @@
         <v>3.3698</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.9873</v>
+        <v>-0.9782</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1837</v>
+        <v>-0.2237</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.1711</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="V28" t="n">
         <v>-2.4675</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-10.4393</v>
+        <v>-10.6417</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.9224</v>
+        <v>-8.228</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.5169</v>
+        <v>-2.4137</v>
       </c>
       <c r="G29" t="n">
         <v>-7.0012</v>
@@ -2716,13 +2716,13 @@
         <v>3.9645</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.6247</v>
+        <v>-1.8271</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.3154</v>
+        <v>-0.621</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.3092</v>
+        <v>-1.2061</v>
       </c>
       <c r="V29" t="n">
         <v>-2.8045</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-38.9705</v>
+        <v>-37.6123</v>
       </c>
       <c r="E30" t="n">
-        <v>-28.3529</v>
+        <v>-28.3527</v>
       </c>
       <c r="F30" t="n">
-        <v>-10.6179</v>
+        <v>-9.259500000000001</v>
       </c>
       <c r="G30" t="n">
         <v>-24.2561</v>
@@ -2770,7 +2770,7 @@
         <v>-4.7235</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.2603</v>
+        <v>-5.260300000000001</v>
       </c>
       <c r="L30" t="n">
         <v>0.5365999999999997</v>
@@ -2791,16 +2791,16 @@
         <v>-23.7866</v>
       </c>
       <c r="R30" t="n">
-        <v>25.769</v>
+        <v>25.76900000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>-10.0576</v>
+        <v>-8.6995</v>
       </c>
       <c r="T30" t="n">
-        <v>-1.779</v>
+        <v>-1.7787</v>
       </c>
       <c r="U30" t="n">
-        <v>-8.2789</v>
+        <v>-6.9209</v>
       </c>
       <c r="V30" t="n">
         <v>-6.639</v>
